--- a/docs/design-vi/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
@@ -1539,7 +1539,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1555,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2078,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2851,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6484,7 +6484,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -9101,7 +9101,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Kiểm tra các mục của vùng tìm kiếm chi tiết được mở rộng (引落元口座支店コード, 引落元口座支店名, 連絡先１, メールアドレス, 請求開始月, 適用日, 支払方法)
+            <t xml:space="preserve">Kiểm tra các mục của vùng tìm kiếm chi tiết được mở rộng (引落元口座支店, 連絡先, メールアドレス, 請求開始月, 適用日, 支払方法, 郵送区分, 新聞単価, 備考)
 </t>
           </r>
           <r>
@@ -9178,7 +9178,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">引落元口座支店コード, 引落元口座支店名, 連絡先１, メールアドレス, 請求開始月, 適用日 (2 ô input bắt đầu・kết thúc), 支払方法 (radio 7 lựa chọn: 口座引落・現金集金・振込集金・JA施設等・給与天引き・クレジットカード・その他) được hiển thị
+            <t xml:space="preserve">引落元口座支店, 連絡先, メールアドレス, 請求開始月 (2 ô input bắt đầu・kết thúc・chọn tháng YYYYMM), 適用日 (2 ô input bắt đầu・kết thúc), 支払方法 (radio 7 lựa chọn: 口座引落・現金集金・振込集金・JA施設等・給与天引き・クレジットカード・その他), 郵送区分 (dropdown: 0:空 / 1:郵送), 新聞単価 (dropdown), 備考 (text・partial match) được hiển thị
 </t>
           </r>
           <r>
@@ -11213,7 +11213,7 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>Giá trị biên độ dài tối đa mục tìm kiếm chi tiết (引落元口座支店コード 3 ký tự, 請求開始月 6 ký tự, 連絡先１ 15 ký tự)</t>
+          <t>Giá trị biên độ dài tối đa mục tìm kiếm chi tiết (引落元口座支店 100 ký tự, 請求開始月 (bắt đầu) YYYYMM 6 chữ số, 連絡先 15 ký tự)</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -11247,7 +11247,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập 3 ký tự vào 引落元口座支店コード, click「検索」, tiếp tục nhập 4 ký tự, click「検索」
+            <t xml:space="preserve">Nhập 100 ký tự vào 引落元口座支店, click「検索」, tiếp tục nhập 101 ký tự, click「検索」
 </t>
           </r>
           <r>
@@ -11264,7 +11264,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập 6 ký tự vào 請求開始月, click「検索」, tiếp tục nhập 7 ký tự, click「検索」
+            <t xml:space="preserve">Nhập 6 chữ số (YYYYMM) vào 請求開始月 (bắt đầu), click「検索」, tiếp tục nhập 7 chữ số, click「検索」
 </t>
           </r>
           <r>
@@ -11281,7 +11281,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Nhập 15 ký tự vào 連絡先１, click「検索」, tiếp tục nhập 16 ký tự, click「検索」</t>
+            <t>Nhập 15 ký tự vào 連絡先, click「検索」, tiếp tục nhập 16 ký tự, click「検索」</t>
           </r>
         </is>
       </c>
@@ -11307,7 +11307,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">3 ký tự tìm kiếm bình thường với HTTP 200, 4 ký tự hiển thị lỗi vượt quá số ký tự (`error_code: VALIDATION_ERROR`, `errors[]` có `field: jastem_toriatsukai_tenpo_code`)
+            <t xml:space="preserve">100 ký tự tìm kiếm bình thường với HTTP 200, 101 ký tự hiển thị lỗi vượt quá số ký tự (`error_code: VALIDATION_ERROR`, `errors[]` có `field: bank_branch`)
 </t>
           </r>
           <r>
@@ -11324,7 +11324,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">6 ký tự tìm kiếm bình thường với HTTP 200, 7 ký tự hiển thị lỗi vượt quá số ký tự (`errors[]` có `field: seikyu_kaishi_month`)
+            <t xml:space="preserve">6 chữ số (YYYYMM) tìm kiếm bình thường với HTTP 200, 7 chữ số hiển thị lỗi định dạng (`請求開始月はYYYYMMの形式で指定してください。`) (`errors[]` có `field: seikyu_kaishi_month_from`)
 </t>
           </r>
           <r>
@@ -11341,7 +11341,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">15 ký tự tìm kiếm bình thường với HTTP 200, 16 ký tự hiển thị lỗi vượt quá số ký tự (`errors[]` có `field: renrakusaki_1`)
+            <t xml:space="preserve">15 ký tự tìm kiếm bình thường với HTTP 200, 16 ký tự hiển thị lỗi vượt quá số ký tự (`errors[]` có `field: renrakusaki`)
 </t>
           </r>
           <r>
@@ -11358,15 +11358,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・引落元口座支店コード là partial match với cột vật lý `bank_branch_code` (tối đa 3 ký tự)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・引落元口座支店名 là partial match với cột vật lý `bank_branch_name` (tối đa 100 ký tự)
+            <t xml:space="preserve">・引落元口座支店 là OR partial match với cột vật lý `bank_branch_code` / `bank_branch_name` (tối đa 100 ký tự)
 </t>
           </r>
           <r>
@@ -14707,7 +14699,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200 (response `{ "message": "購読者を削除しました。" }`, toast `購読者を削除しました。`)
+            <t xml:space="preserve">Trả về HTTP 200 (response `{ "message": "削除しました。" }`, toast `削除しました。`)
 </t>
           </r>
           <r>
@@ -15789,7 +15781,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Tên file là `dokusya_export_YYYYMMDD_HHmmss.xlsx` (JST), `Content-Type` là `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`, dòng header là `管理支店, 支店, 組合員コード, 購読者名, 連絡先１, 連絡先２, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 購読開始日, 購読中止日` (12 cột)
+            <t xml:space="preserve">Tên file là `購読者一覧出力_YYYYMMDD_HHmmss.xlsx` (JST), `Content-Type` là `application/vnd.openxmlformats-officedocument.spreadsheetml.sheet`, dòng header là `管理支店, 支店, 組合員コード, 購読者名, 連絡先１, 連絡先２, 配達先郵便, 配達先住所, 販売店コード, 販売店名, 購読開始日, 購読中止日` (12 cột)
 </t>
           </r>
           <r>

--- a/docs/design-vi/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-014/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者明細検索画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Bổ sung 7 ca kiểm thử (044〜050): thay đổi・hủy bỏ đặt trước ngừng đọc báo của bản điện tử (#56087, 5 ca — đồng bộ với bản tiếng Nhật), hiển thị tổng số bản "全 M 部" bên cạnh "全 N 件" (#56240), và giới hạn chỉ bản giấy mới được xóa (#56422)</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,7 +1599,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1615,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2138,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2911,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2927,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ59"/>
+  <dimension ref="A1:BQ67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6484,7 +6544,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Tran Duc Tuyen</t>
+          <t>Kieu Thi Diem</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -18065,8 +18125,720 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo・Hiển thị tổng số bản・Giới hạn xóa (Function — Stop / Total-busu / Delete)</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="10" t="n"/>
+      <c r="AM60" s="10" t="n"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="10" t="n"/>
+      <c r="AP60" s="10" t="n"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="10" t="n"/>
+      <c r="AS60" s="10" t="n"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="10" t="n"/>
+      <c r="AV60" s="10" t="n"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="10" t="n"/>
+      <c r="AY60" s="10" t="n"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="10" t="n"/>
+      <c r="BB60" s="10" t="n"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="10" t="n"/>
+      <c r="BE60" s="10" t="n"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="10" t="n"/>
+      <c r="BH60" s="10" t="n"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="10" t="n"/>
+      <c r="BK60" s="10" t="n"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="144" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-044</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo — Bản điện tử: tháng kết thúc đang đặt trước được khôi phục trong popup</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: người đọc bản điện tử (`dokusya_id=1020, dokusya_shubetsu=2, shiharai_hoho≠6, seikyu_kaishi_month='202604'`) đã đăng ký đặt trước hủy vào 2030/07 (batch ngày đến hạn chưa chạy ＝ `kaiyaku_flg=false`)</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr"/>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="112" customHeight="1">
+      <c r="A62" s="44" t="n">
+        <v>45</v>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-045</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo — Bản điện tử: chọn lại tháng kết thúc để thay đổi đặt trước</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: giống ACSMS-TC-014-044 (có đặt trước hủy 2030/07)
+・Liên kết bản điện tử (DENSHIBAN_PUSH_ENABLED=true) đang bật</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="46" t="inlineStr"/>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="10" t="n"/>
+      <c r="T62" s="10" t="n"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="46" t="inlineStr"/>
+      <c r="Y62" s="10" t="n"/>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="45" t="inlineStr"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="45" t="inlineStr"/>
+      <c r="AK62" s="10" t="n"/>
+      <c r="AL62" s="11" t="n"/>
+      <c r="AM62" s="45" t="inlineStr"/>
+      <c r="AN62" s="10" t="n"/>
+      <c r="AO62" s="11" t="n"/>
+      <c r="AP62" s="45" t="inlineStr"/>
+      <c r="AQ62" s="10" t="n"/>
+      <c r="AR62" s="11" t="n"/>
+      <c r="AS62" s="45" t="inlineStr"/>
+      <c r="AT62" s="10" t="n"/>
+      <c r="AU62" s="11" t="n"/>
+      <c r="AV62" s="45" t="inlineStr"/>
+      <c r="AW62" s="10" t="n"/>
+      <c r="AX62" s="11" t="n"/>
+      <c r="AY62" s="45" t="inlineStr"/>
+      <c r="AZ62" s="10" t="n"/>
+      <c r="BA62" s="11" t="n"/>
+      <c r="BB62" s="45" t="inlineStr"/>
+      <c r="BC62" s="10" t="n"/>
+      <c r="BD62" s="11" t="n"/>
+      <c r="BE62" s="45" t="inlineStr"/>
+      <c r="BF62" s="10" t="n"/>
+      <c r="BG62" s="11" t="n"/>
+      <c r="BH62" s="45" t="inlineStr"/>
+      <c r="BI62" s="10" t="n"/>
+      <c r="BJ62" s="11" t="n"/>
+      <c r="BK62" s="46" t="inlineStr"/>
+      <c r="BL62" s="10" t="n"/>
+      <c r="BM62" s="10" t="n"/>
+      <c r="BN62" s="10" t="n"/>
+      <c r="BO62" s="10" t="n"/>
+      <c r="BP62" s="10" t="n"/>
+      <c r="BQ62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="112" customHeight="1">
+      <c r="A63" s="44" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-046</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo — Bản điện tử: xóa trống tháng kết thúc để hủy đặt trước</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: giống ACSMS-TC-014-044 (có đặt trước hủy 2030/07)
+・Liên kết bản điện tử (DENSHIBAN_PUSH_ENABLED=true) đang bật</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="46" t="inlineStr"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="46" t="inlineStr"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="45" t="inlineStr"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="45" t="inlineStr"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="11" t="n"/>
+      <c r="AM63" s="45" t="inlineStr"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="11" t="n"/>
+      <c r="AP63" s="45" t="inlineStr"/>
+      <c r="AQ63" s="10" t="n"/>
+      <c r="AR63" s="11" t="n"/>
+      <c r="AS63" s="45" t="inlineStr"/>
+      <c r="AT63" s="10" t="n"/>
+      <c r="AU63" s="11" t="n"/>
+      <c r="AV63" s="45" t="inlineStr"/>
+      <c r="AW63" s="10" t="n"/>
+      <c r="AX63" s="11" t="n"/>
+      <c r="AY63" s="45" t="inlineStr"/>
+      <c r="AZ63" s="10" t="n"/>
+      <c r="BA63" s="11" t="n"/>
+      <c r="BB63" s="45" t="inlineStr"/>
+      <c r="BC63" s="10" t="n"/>
+      <c r="BD63" s="11" t="n"/>
+      <c r="BE63" s="45" t="inlineStr"/>
+      <c r="BF63" s="10" t="n"/>
+      <c r="BG63" s="11" t="n"/>
+      <c r="BH63" s="45" t="inlineStr"/>
+      <c r="BI63" s="10" t="n"/>
+      <c r="BJ63" s="11" t="n"/>
+      <c r="BK63" s="46" t="inlineStr"/>
+      <c r="BL63" s="10" t="n"/>
+      <c r="BM63" s="10" t="n"/>
+      <c r="BN63" s="10" t="n"/>
+      <c r="BO63" s="10" t="n"/>
+      <c r="BP63" s="10" t="n"/>
+      <c r="BQ63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="144" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-047</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo — Sau khi hủy đăng ký đã xác định thì không thể thay đổi・hủy bỏ</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: người đọc bản điện tử (`dokusya_id=1021, dokusya_shubetsu=2`) đã có việc hủy đăng ký được batch ngày đến hạn xác định (có dòng hủy thực tế với `kaiyaku_flg=true`・`tetsuzuki_shurui=0`)</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr"/>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="144" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-048</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>Ngừng đọc báo — Hộp thoại xác nhận cuối cùng (Có／Không)</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN
+・Dữ liệu chuẩn bị: người đọc bản giấy (`dokusya_id=1022, dokusya_shubetsu=1`／không có đặt trước hủy), người đọc bản điện tử (`dokusya_id=1020, dokusya_shubetsu=2, seikyu_kaishi_month='202604'`／có đặt trước hủy 2030/07)</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="192" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-049</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>Kết quả tìm kiếm — Hiển thị tổng số bản đọc "全 M 部" bên cạnh "全 N 件" (#56240)</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100)
+・JA của mình có từ 25 người đọc trở lên, và tổng `dokusya_busu` khác với tổng của 1 trang (ví dụ: 25 bản ghi・tổng 40 bản, tổng của 20 bản ghi ở trang 1 là 32 bản)
+・Trong đó có người đọc sở hữu nhiều dòng lịch sử (dùng để kiểm chứng trùng lặp khi lọc theo ngày áp dụng)</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr"/>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="240" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-014-050</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>Xóa — Chỉ bản giấy mới được xóa (#56422)</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN (thuộc ja_id=100, có quyền `dokusya.delete`)
+・JA của mình có các người đọc sau:
+・(a) Bản giấy (dokusya_shubetsu=1)
+・(b) Bản điện tử・phương thức thanh toán=trích nợ tài khoản (không phải thẻ tín dụng)
+・(c) Bản điện tử・thanh toán bằng thẻ tín dụng
+・(d) Kết hợp (dokusya_shubetsu=3)</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr"/>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="802">
+  <mergeCells count="922">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
@@ -18079,20 +18851,25 @@
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="AV57:AX57"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
@@ -18126,12 +18903,14 @@
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
     <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
+    <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="BB27:BD27"/>
@@ -18141,18 +18920,27 @@
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
     <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AS62:AU62"/>
+    <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="AP53:AR53"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="AS64:AU64"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="J65:P65"/>
+    <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
@@ -18167,6 +18955,7 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -18223,7 +19012,10 @@
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
+    <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
     <mergeCell ref="AP44:AR44"/>
@@ -18234,22 +19026,28 @@
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="BB59:BD59"/>
+    <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="X27:AD27"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
+    <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
     <mergeCell ref="Q51:W51"/>
     <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
     <mergeCell ref="AP24:AR24"/>
@@ -18270,6 +19068,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="J21:P21"/>
     <mergeCell ref="A1:E1"/>
@@ -18286,6 +19085,7 @@
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
+    <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="X40:AD40"/>
@@ -18301,10 +19101,13 @@
     <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="J49:P49"/>
     <mergeCell ref="J36:P36"/>
+    <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
     <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
@@ -18314,10 +19117,13 @@
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
+    <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
@@ -18327,6 +19133,7 @@
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -18344,6 +19151,7 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="AG51:AI51"/>
@@ -18356,10 +19164,12 @@
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
@@ -18369,25 +19179,34 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="AS43:AU43"/>
+    <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
     <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="BH67:BJ67"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
     <mergeCell ref="J42:P42"/>
+    <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="AG19:AI19"/>
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="X67:AD67"/>
     <mergeCell ref="J37:P37"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="Q33:W33"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
@@ -18399,7 +19218,9 @@
     <mergeCell ref="E45:I45"/>
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
+    <mergeCell ref="X62:AD62"/>
     <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="BB19:BD19"/>
@@ -18409,10 +19230,14 @@
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="J32:P32"/>
+    <mergeCell ref="J63:P63"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
@@ -18433,8 +19258,10 @@
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
     <mergeCell ref="Q21:W21"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
@@ -18454,6 +19281,7 @@
     <mergeCell ref="AM46:AO46"/>
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="AJ23:AL23"/>
+    <mergeCell ref="E66:I66"/>
     <mergeCell ref="E53:I53"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
@@ -18464,6 +19292,7 @@
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="J51:P51"/>
     <mergeCell ref="F2:Q2"/>
@@ -18492,17 +19321,22 @@
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="AY27:BA27"/>
     <mergeCell ref="AJ31:AL31"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="Q29:W29"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="AV59:AX59"/>
+    <mergeCell ref="AP62:AR62"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -18510,15 +19344,22 @@
     <mergeCell ref="AS50:AU50"/>
     <mergeCell ref="E10:I11"/>
     <mergeCell ref="BK56:BQ56"/>
+    <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
     <mergeCell ref="AE59:AF59"/>
@@ -18528,9 +19369,11 @@
     <mergeCell ref="AE46:AF46"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -18574,11 +19417,13 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
@@ -18588,20 +19433,29 @@
     <mergeCell ref="BE42:BG42"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="AS66:AU66"/>
     <mergeCell ref="E19:I19"/>
+    <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
+    <mergeCell ref="AE67:AF67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
     <mergeCell ref="AJ32:AL32"/>
+    <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
+    <mergeCell ref="Q63:W63"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -18619,6 +19473,7 @@
     <mergeCell ref="AS21:AU21"/>
     <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
+    <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
     <mergeCell ref="AE16:AF16"/>
     <mergeCell ref="AG32:AI32"/>
@@ -18640,6 +19495,7 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
+    <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
@@ -18668,6 +19524,7 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -18676,6 +19533,9 @@
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
     <mergeCell ref="BE59:BG59"/>
+    <mergeCell ref="AY62:BA62"/>
+    <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -18683,7 +19543,9 @@
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
     <mergeCell ref="AV19:AX19"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
     <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
@@ -18708,6 +19570,7 @@
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
@@ -18720,6 +19583,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -18728,6 +19592,7 @@
     <mergeCell ref="BK33:BQ33"/>
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
+    <mergeCell ref="BH62:BJ62"/>
     <mergeCell ref="AV38:AX38"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="AY39:BA39"/>
@@ -18743,10 +19608,12 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="AS37:AU37"/>
     <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="J38:P38"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
@@ -18759,17 +19626,26 @@
     <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
+    <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
+    <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BB66:BD66"/>
+    <mergeCell ref="Q67:W67"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
     <mergeCell ref="E54:I54"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
+    <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
+    <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
@@ -18778,6 +19654,7 @@
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
     <mergeCell ref="E43:I43"/>
+    <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
     <mergeCell ref="AE20:AF20"/>
@@ -18786,10 +19663,12 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="A60:BQ60"/>
     <mergeCell ref="AS27:AU27"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
+    <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
@@ -18798,11 +19677,15 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
@@ -18821,25 +19704,30 @@
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
+    <mergeCell ref="BH63:BJ63"/>
     <mergeCell ref="AJ42:AL42"/>
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="X55:AD55"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="BE17:BG17"/>
@@ -18847,9 +19735,12 @@
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BE19:BG19"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
@@ -18863,6 +19754,7 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="AG10:AU10"/>
     <mergeCell ref="AG44:AI44"/>
+    <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="AM28:AO28"/>
@@ -18871,13 +19763,13 @@
     <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE34 AE36:AE51 AE53:AE59 AE61:AE67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG34 AG36:AG51 AG53:AG59 AG61:AG67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV34 AV36:AV51 AV53:AV59 AV61:AV67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
